--- a/data/filtered_data.xlsx
+++ b/data/filtered_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,413 +455,409 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>749357735</v>
+        <v>760718345</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто серое классика</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BUTALABEL</t>
+          <t>SANNARA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>459</v>
       </c>
       <c r="F2" t="n">
-        <v>8935</v>
+        <v>4092</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/749357735/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/760718345/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>500291585</v>
+        <v>174345726</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Двубортное пальто из драпа с добавлением шерсти</t>
+          <t>Пальто длинное демисезонное оверсайз</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELA</t>
+          <t>Amore Wear</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>4.8</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>4926</v>
       </c>
       <c r="F3" t="n">
-        <v>4032</v>
+        <v>5275</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/500291585/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/174345726/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>305471553</v>
+        <v>771425157</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Пальто длинное демисезонное</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Befur</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="F4" t="n">
-        <v>8062</v>
+        <v>8156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/305471553/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/771425157/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>174345729</v>
+        <v>749357735</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Пальто длинное демисезонное оверсайз</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amore Wear</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>4.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4221</v>
+        <v>188</v>
       </c>
       <c r="F5" t="n">
-        <v>4816</v>
+        <v>8156</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/174345729/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/749357735/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>669906164</v>
+        <v>481144266</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+          <t>Пальто шерстяное демисезонное длинное серое</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>8083</v>
+        <v>8388</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/669906164/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144266/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107713204</v>
+        <v>749357736</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Пальто демисезонное прямое</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5 LOVE</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>4.8</v>
       </c>
       <c r="E7" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="F7" t="n">
-        <v>9800</v>
+        <v>8754</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/107713204/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/749357736/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>488387893</v>
+        <v>760720575</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Пальто весна-осень макси в полоску</t>
+          <t>Пальто серое классика</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>SANNARA</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>4.8</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>459</v>
       </c>
       <c r="F8" t="n">
-        <v>5153</v>
+        <v>4344</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488387893/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/760720575/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>532253417</v>
+        <v>316269562</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Пальто короткое шерстяное с воротником</t>
+          <t>Пальто весеннее длинное оверсайз</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="F9" t="n">
-        <v>7818</v>
+        <v>7929</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/532253417/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/316269562/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>620460183</v>
+        <v>628377836</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Пальто пиджак демисезонное</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LYNAE</t>
-        </is>
-      </c>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>4389</v>
+        <v>4375</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/620460183/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/628377836/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>171721084</v>
+        <v>158589195</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Пальто демисезонное осеннее леопард длинное</t>
+          <t>Пальто кокон шерстяное</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MAXLOVE</t>
+          <t>GalaGrosso</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>4.7</v>
       </c>
       <c r="E11" t="n">
-        <v>1257</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>8913</v>
+        <v>3091</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/171721084/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/158589195/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>497508666</v>
+        <v>452838723</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Пальто шерстяное короткое жакет</t>
+          <t>Пальто темно серое классическое длинное</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>SANNARA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="F12" t="n">
-        <v>7672</v>
+        <v>3260</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/452838723/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>235923966</v>
+        <v>481144243</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Пальто черное с поясом удлиненное</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cassidy</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>549</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>7567</v>
+        <v>9227</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/235923966/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144243/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>139833751</v>
+        <v>488387893</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Пальто зимнее с утеплителем меховое</t>
+          <t>Пальто весна-осень макси в полоску</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5 LOVE</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>8652</v>
+        <v>6680</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/139833751/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488387893/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>287755147</v>
+        <v>497508664</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Пальто двубортное драповое с шерстью демисезонное</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Befree</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E15" t="n">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>3783</v>
+        <v>6901</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/287755147/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497508664/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>312859709</v>
+        <v>310057846</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -870,883 +866,1252 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KUMAIBA</t>
+          <t>Alexander Serov</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>4.8</v>
       </c>
       <c r="E16" t="n">
-        <v>215</v>
+        <v>1778</v>
       </c>
       <c r="F16" t="n">
-        <v>4478</v>
+        <v>5528</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/312859709/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/310057846/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>236223618</v>
+        <v>825019950</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Укороченное пальто</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FANCY CODE</t>
+          <t>BUTALABEL</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>4.8</v>
       </c>
       <c r="E17" t="n">
-        <v>659</v>
+        <v>188</v>
       </c>
       <c r="F17" t="n">
-        <v>3351</v>
+        <v>9788</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/236223618/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/825019950/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>591306301</v>
+        <v>502427212</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Пальто макси приталенное длинное зима</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>Пальто демисезонное</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SerpikovaNS</t>
+        </is>
+      </c>
       <c r="D18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>4833</v>
+        <v>5054</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/591306301/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/502427212/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>754801836</v>
+        <v>516995752</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Полупальто двубортное драп</t>
+          <t>Пальто осеннее длинное</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INTUITIV</t>
+          <t>MÁS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>3966</v>
+        <v>8870</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/754801836/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/516995752/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>322555095</v>
+        <v>488386749</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Пальто шерстяное длинное</t>
+          <t>Пальто длинное оверсайз весна-осень в полоску</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MAXI STUDIO</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>5269</v>
+        <v>6293</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/322555095/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488386749/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>575454880</v>
+        <v>306851990</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Пальто зимнее на верблюжьей шерсти больших размеров</t>
+          <t>Пальто длинное демисезонное прямое с поясом</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FABRI</t>
+          <t>Willines</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>4.8</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="F21" t="n">
-        <v>5586</v>
+        <v>5194</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/575454880/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/306851990/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>567335698</v>
+        <v>481144278</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Полупальто короткое демисезонное для невысокого роста</t>
+          <t>Пальто шерстяное весна-осень длинное</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Calista</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="F22" t="n">
-        <v>7003</v>
+        <v>8947</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/567335698/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144278/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40807839</v>
+        <v>669906159</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Пальто весеннее оверсайз</t>
+          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>g-pride</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="E23" t="n">
-        <v>540</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>2536</v>
+        <v>7581</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/40807839/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/669906159/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>603926419</v>
+        <v>10674551</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Пальто длинное весеннее большие размеры оверсайз с поясом</t>
+          <t>Пальто плюс сайз с поясом демисезонное удлиненное</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>Cassidy</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="F24" t="n">
-        <v>8673</v>
+        <v>8327</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/603926419/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/10674551/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>307536490</v>
+        <v>322552655</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Шерстяное пальто весеннее короткое</t>
+          <t>Пальто женское весна осень</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Marco Bay</t>
+          <t>MAXI STUDIO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>5862</v>
+        <v>4805</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/307536490/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/322552655/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>292873097</v>
+        <v>467538239</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Короткое шерстяное пальто</t>
+          <t>Пальто коричневое весна-осень длинное оверсайз</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>Giulia Rosetti</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>2991</v>
       </c>
       <c r="F26" t="n">
-        <v>6326</v>
+        <v>9900</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/292873097/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/467538239/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>514701286</v>
+        <v>497841892</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Пальто шерстяное классическое прямое базовое</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>TOM TAILOR</t>
-        </is>
-      </c>
+          <t>Пальто Шерстяное приталенное серое</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>8631</v>
+        <v>9059</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/514701286/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497841892/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>319079863</v>
+        <v>481144228</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+          <t>Пальто шерстяное весна-осень длинное</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Roman fashion</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E28" t="n">
-        <v>662</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>9452</v>
+        <v>9903</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/319079863/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144228/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>171651840</v>
+        <v>167341416</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Пальто женское демисезонное гусиная лапка с поясом шерстяное</t>
+          <t>Пальто классическое демисезонное</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Soréa</t>
+          <t>WORLD VOGUE</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1211</v>
+        <v>118</v>
       </c>
       <c r="F29" t="n">
-        <v>8224</v>
+        <v>6298</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/171651840/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/167341416/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>205498991</v>
+        <v>174345729</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Двубортное укороченное пальто</t>
+          <t>Пальто длинное демисезонное оверсайз</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ELIS</t>
+          <t>Amore Wear</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>4470</v>
       </c>
       <c r="F30" t="n">
-        <v>7142</v>
+        <v>5275</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/205498991/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/174345729/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>446790066</v>
+        <v>500291585</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Пальто с поясом удлиненное большое</t>
+          <t>Двубортное пальто из драпа с добавлением шерсти</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cassidy</t>
+          <t>SELA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E31" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="F31" t="n">
-        <v>7262</v>
+        <v>4453</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/446790066/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/500291585/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>669906167</v>
+        <v>642416346</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+          <t>Пальто халат демисезонное приталенное</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>Calista</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>9042</v>
+        <v>7786</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/669906167/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/642416346/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>439112780</v>
+        <v>218700008</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+          <t>Пальто длинное демисезонное оверсайз</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>KUMAYIBA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>439</v>
       </c>
       <c r="F33" t="n">
-        <v>7813</v>
+        <v>4811</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/439112780/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/218700008/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>723223863</v>
+        <v>481144253</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Пальто весеннее длинное оверсайз</t>
+          <t>Пальто шерстяное демисезонное длинное</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>TRIUMF ST</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F34" t="n">
-        <v>7948</v>
+        <v>8388</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/723223863/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/481144253/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>263567522</v>
+        <v>10674550</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Пальто женское весна-осень длинное</t>
+          <t>Пальто оверсайз с поясом демисезонное удлиненное</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No name’ just quality</t>
+          <t>Cassidy</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="F35" t="n">
-        <v>6850</v>
+        <v>8855</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/263567522/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/10674550/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>681322900</v>
+        <v>452839060</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Пальто шерстяное классическое прямое базовое</t>
+          <t>Пальто коричневое классическое</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TOM TAILOR</t>
+          <t>SANNARA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="F36" t="n">
-        <v>9569</v>
+        <v>3177</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/681322900/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/452839060/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>806502486</v>
+        <v>497508666</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Короткое двубортное женское полупальто из смесовой шерсти</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SELA</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
-        <v>7672</v>
+        <v>7407</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/806502486/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>749357736</v>
+        <v>278824636</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное длинное</t>
+          <t>Пальто демисезонное большие размеры</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUTALABEL</t>
+          <t>FANCY CODE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E38" t="n">
-        <v>200</v>
+        <v>820</v>
       </c>
       <c r="F38" t="n">
-        <v>8727</v>
+        <v>9207</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/749357736/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/278824636/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>439112782</v>
+        <v>211322127</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+          <t>Пальто длинное демисезонное оверсайз</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>the nana</t>
+          <t>Amore Wear</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>1754</v>
       </c>
       <c r="F39" t="n">
-        <v>7948</v>
+        <v>4969</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/439112782/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/211322127/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>785074282</v>
+        <v>666480761</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Женское полупальто</t>
+          <t>Пальто весеннее длинное оверсайз</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>9786</v>
+        <v>6291</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/785074282/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/666480761/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>61911066</v>
+        <v>498046112</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Пальто длинное демисезонное оверсайз из шерсти</t>
+          <t>Полупальто женское</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TO BE ONE</t>
+          <t>VeraVictory</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="E41" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="F41" t="n">
-        <v>9757</v>
+        <v>6024</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/61911066/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/498046112/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>458555575</v>
+        <v>701642828</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Полупальто демисезонное модное оверсайз</t>
+          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Мисс Данин</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F42" t="n">
-        <v>7394</v>
+        <v>5777</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/458555575/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/701642828/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>163566992</v>
+        <v>621862264</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Пальто весеннее шерстяное кимоно без подклада оверсайз</t>
+          <t>Пальто оверсайз длинное весеннее</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VESHALKA</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E43" t="n">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="F43" t="n">
-        <v>6293</v>
+        <v>7391</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/163566992/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/621862264/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>544897605</v>
+        <v>723223859</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Пальто шерстяное весна-осень</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Пальто весеннее длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
       <c r="D44" t="n">
         <v>4.9</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" t="n">
-        <v>6982</v>
+        <v>5778</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/544897605/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/723223859/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>141816944</v>
+        <v>263567534</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Удлиненное пальто женское демисезонное классика</t>
+          <t>Пальто женское весна-осень длинное</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MEROS TEX</t>
+          <t>No name’ just quality</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="E45" t="n">
-        <v>472</v>
+        <v>8</v>
       </c>
       <c r="F45" t="n">
-        <v>3068</v>
+        <v>3651</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/141816944/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/263567534/detail.aspx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>241700498</v>
+        <v>669906166</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Пальто зимнее</t>
+          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FUBIARE</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5777</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/669906166/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>621862265</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Пальто оверсайз длинное весеннее</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8399</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/621862265/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>287694148</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Полупальто шерстяное</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7603</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/287694148/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>366417625</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>4.9</v>
       </c>
-      <c r="E46" t="n">
-        <v>32</v>
-      </c>
-      <c r="F46" t="n">
-        <v>7995</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.wildberries.ru/catalog/241700498/detail.aspx</t>
+      <c r="E49" t="n">
+        <v>13</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7603</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/366417625/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>258010077</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ZA_I_RA_MODA 369</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>290</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6206</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/258010077/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>595049394</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7368</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/595049394/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>742440411</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Пальто весеннее миди на пуговицах с поясом</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6720</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/742440411/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>544897605</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8043</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/544897605/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>439117400</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>75</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6241</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/439117400/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>544042705</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>15</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8020</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/544042705/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>170124498</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Пальто весна осень шерстяное</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Стиль вкуса</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E56" t="n">
+        <v>358</v>
+      </c>
+      <c r="F56" t="n">
+        <v>7342</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/170124498/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>723223861</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7797</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/723223861/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>669906163</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5535</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/669906163/detail.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>273571239</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Пальто женское драповое демисезонное</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Jam Deallies</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5633</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/273571239/detail.aspx</t>
         </is>
       </c>
     </row>
